--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00967B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00967B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B6021D3-7A72-4BA5-AB37-7B1C927A83D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EDA6D2F-D902-49FE-8A6E-370A8B1E4E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B5E9A752-76F3-4C77-BEBE-0CCEF7371C6E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{79C9D61B-52AC-4BAC-B36A-2FE5123FD528}"/>
   </bookViews>
   <sheets>
     <sheet name="00967B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1549,24 +1549,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5ED388E-1872-40E2-8C4A-C661569D5C3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0619287-215F-4FBA-9495-FB32A3A3FB4D}">
   <dimension ref="A1:R21"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1594,7 +1595,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1624,7 +1625,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1670,7 +1671,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1720,7 +1721,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v>4.24</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1800,7 +1801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1856,7 +1857,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1912,7 +1913,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -1966,7 +1967,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2022,7 +2023,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2078,7 +2079,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2134,7 +2135,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2190,7 +2191,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2246,7 +2247,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2302,7 +2303,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2358,7 +2359,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2414,7 +2415,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2470,7 +2471,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2526,7 +2527,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2582,7 +2583,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="51" t="s">
         <v>54</v>
       </c>
